--- a/output/pdf_financials_xlsx/HVG.xlsx
+++ b/output/pdf_financials_xlsx/HVG.xlsx
@@ -1207,7 +1207,7 @@
         <v>-1.468257</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.206999</v>
+        <v>-0.206999</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.842498</v>
@@ -1479,7 +1479,7 @@
         <v>-1.418757</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.206999</v>
+        <v>-0.206999</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.842498</v>
@@ -1641,7 +1641,7 @@
         <v>-1.418757</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.206999</v>
+        <v>-0.206999</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.842498</v>
@@ -1803,7 +1803,7 @@
         <v>70.93785</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>6.899967</v>
+        <v>-6.899967</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>7.677075</v>
@@ -1865,7 +1865,7 @@
         <v>-1.468257</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.206999</v>
+        <v>-0.206999</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.842498</v>
@@ -1973,7 +1973,7 @@
         <v>-1.468257</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.206999</v>
+        <v>-0.206999</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.842498</v>
@@ -2109,7 +2109,7 @@
         <v>-3.371344389980773</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -5334,10 +5334,10 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.000142</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.000187</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0</v>
@@ -5380,43 +5380,43 @@
         <v>1.329398</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.329398</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.329398</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.329398</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.329398</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.572378</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.584466</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.724249</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.724249</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.949436</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.296053</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.296053</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.296053</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.297836</v>
       </c>
     </row>
     <row r="93">
@@ -5712,10 +5712,10 @@
         <v>0.052347</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.672574</v>
+        <v>-0.672574</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.505668</v>
+        <v>-0.505668</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-1.180582</v>
@@ -6761,13 +6761,13 @@
         </is>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.141737</v>
+        <v>-0.305939</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.17045</v>
+        <v>0.06047</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>2.253767</v>
+        <v>1.792874</v>
       </c>
     </row>
     <row r="119">
@@ -8547,7 +8547,11 @@
           <t>Share‐based payment reserve 8</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -9338,7 +9342,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10099,7 +10107,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11076,7 +11088,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -11349,7 +11365,11 @@
           <t>Investment revaluation reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12170,7 +12190,11 @@
           <t>Share‐based payment reserve 10</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -12259,7 +12283,11 @@
           <t>Investment revaluation reserve 4</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -12815,7 +12843,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12904,7 +12936,11 @@
           <t>Investment revaluation reserve 4</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14014,7 +14050,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16160,10 +16200,10 @@
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>0.672574</v>
+        <v>-0.672574</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>0.505668</v>
+        <v>-0.505668</v>
       </c>
       <c r="L94" s="5" t="n">
         <v>-1.180582</v>
@@ -16665,7 +16705,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -41311,10 +41355,10 @@
         </is>
       </c>
       <c r="G374" s="5" t="n">
-        <v>0.206999</v>
+        <v>-0.206999</v>
       </c>
       <c r="H374" s="5" t="n">
-        <v>1.842498</v>
+        <v>-1.842498</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -41495,10 +41539,10 @@
         </is>
       </c>
       <c r="G376" s="5" t="n">
-        <v>0.209685</v>
+        <v>-0.209685</v>
       </c>
       <c r="H376" s="5" t="n">
-        <v>1.842498</v>
+        <v>-1.842498</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HVG.xlsx
+++ b/output/pdf_financials_xlsx/HVG.xlsx
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000636</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.759569</v>
+        <v>-4.760205</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.468257</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.759569</v>
+        <v>-4.760205</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.468257</v>
@@ -2246,19 +2246,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.266046</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.12569</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.201608</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.107609</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.061626</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.015559</v>
@@ -2270,25 +2270,25 @@
         <v>0.070733</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.43324</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.137954</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.818213</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.819035</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.514814</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.311837</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.170688</v>
       </c>
     </row>
     <row r="35">
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.008</v>
+        <v>0.274046</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0095</v>
+        <v>1.13519</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.00088</v>
+        <v>0.202488</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.000646</v>
+        <v>0.108255</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.000788</v>
+        <v>0.062414</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.015892</v>
@@ -2374,25 +2374,25 @@
         <v>0.070733</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.43324</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.137954</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.818213</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.819035</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.514814</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.311837</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.170688</v>
       </c>
     </row>
     <row r="37">
@@ -2974,19 +2974,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.270634</v>
+        <v>0.004588</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.146583</v>
+        <v>0.020893</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.205512</v>
+        <v>0.003904</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.111513</v>
+        <v>0.003904</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.061626</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.000917</v>
@@ -2998,25 +2998,25 @@
         <v>0.009948</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.436965</v>
+        <v>0.003725</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.157662</v>
+        <v>0.019708</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.826938</v>
+        <v>0.008725</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.84576</v>
+        <v>0.026725</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.518539</v>
+        <v>0.003725</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.315562</v>
+        <v>0.003725</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.228631</v>
+        <v>0.057943</v>
       </c>
     </row>
     <row r="49">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -42981,7 +42981,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E392" s="5" t="n">
